--- a/projects/project-04-sql-excel-power-bi/excel/manufacturing_controlling.xlsx
+++ b/projects/project-04-sql-excel-power-bi/excel/manufacturing_controlling.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frant\Documents\data-analytics-workspace\da-end-to-end-projects-portfolio\projects\project-04-sql-excel-power-bi\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8667BDD8-0A4B-4264-ACD8-3BC7E15E9F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5B6676-B649-4CD6-9829-E85EBF6D35DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C7CBDF27-E4AB-46F6-958A-6C174B338702}"/>
   </bookViews>
@@ -354,7 +354,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3673" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3674" uniqueCount="645">
   <si>
     <t>zakazka_id</t>
   </si>
@@ -3387,57 +3387,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Po odečtení přiřazených fixních výrobních nákladů a správní a prodejní režie zbývá </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>kalkulovaný zisk 16,20 Kč/ks</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, což odpovídá marži </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5,06 %</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-  </si>
-  <si>
     <t>fixní, předpoklad</t>
   </si>
   <si>
@@ -3547,6 +3496,26 @@
   </si>
   <si>
     <t>Zvýšení zisku (Kč):</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Po odečtení přiřazených fixních výrobních nákladů a správní a prodejní režie zbývá </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kalkulovaný zisk</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> 16,20 Kč/ks, což odpovídá marži 5,06 %. </t>
   </si>
 </sst>
 </file>
@@ -26978,7 +26947,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="38" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="67"/>
@@ -27000,13 +26969,13 @@
     </row>
     <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B3" s="62"/>
       <c r="C3" s="67"/>
       <c r="D3" s="58"/>
       <c r="E3" s="20" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="F3" s="68"/>
       <c r="G3" s="68"/>
@@ -27032,7 +27001,7 @@
       <c r="C5" s="78"/>
       <c r="D5" s="58"/>
       <c r="E5" s="70" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F5" s="74">
         <v>200</v>
@@ -27052,7 +27021,7 @@
       <c r="C6" s="78"/>
       <c r="D6" s="58"/>
       <c r="E6" s="70" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F6" s="75">
         <v>250</v>
@@ -27073,7 +27042,7 @@
       <c r="C7" s="78"/>
       <c r="D7" s="58"/>
       <c r="E7" s="70" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F7" s="76">
         <v>20</v>
@@ -27089,7 +27058,7 @@
       <c r="C8" s="54"/>
       <c r="D8" s="58"/>
       <c r="E8" s="70" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F8" s="75">
         <v>2000</v>
@@ -27130,7 +27099,7 @@
       <c r="C10" s="54"/>
       <c r="D10" s="58"/>
       <c r="E10" s="58" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F10" s="49">
         <f>$B$15</f>
@@ -27150,7 +27119,7 @@
       <c r="C11" s="54"/>
       <c r="D11" s="58"/>
       <c r="E11" s="59" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F11" s="60">
         <f>F5*F10</f>
@@ -27170,7 +27139,7 @@
       <c r="C12" s="54"/>
       <c r="D12" s="58"/>
       <c r="E12" s="58" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F12" s="49">
         <f>F7-F11</f>
@@ -27190,7 +27159,7 @@
       <c r="C13" s="54"/>
       <c r="D13" s="58"/>
       <c r="E13" s="59" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F13" s="64">
         <f>F5*F6</f>
@@ -27208,11 +27177,11 @@
         <v>61.6</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="58" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F14" s="63">
         <f>F5*F9</f>
@@ -27223,7 +27192,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="46" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B15" s="47">
         <f>SUMIFS(PlanPraceKapacity[strojove_hodiny_na_dobry_kus],PlanPraceKapacity[vyrobek_id],$B$5,PlanPraceKapacity[mesic],$B$6)</f>
@@ -27232,7 +27201,7 @@
       <c r="C15" s="54"/>
       <c r="D15" s="58"/>
       <c r="E15" s="77" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F15" s="73">
         <f>F14+F8</f>
@@ -27252,7 +27221,7 @@
       <c r="C16" s="54"/>
       <c r="D16" s="58"/>
       <c r="E16" s="81" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F16" s="80">
         <f>F13-F15</f>
@@ -27278,7 +27247,7 @@
     </row>
     <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="50" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B18" s="73">
         <f>B11+B14+B17</f>
@@ -27301,7 +27270,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="54" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D19" s="58"/>
       <c r="E19" s="48"/>
@@ -27317,11 +27286,11 @@
         <v>15</v>
       </c>
       <c r="C20" s="54" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D20" s="58"/>
       <c r="E20" s="83" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F20" s="83"/>
       <c r="G20" s="83"/>
@@ -27338,7 +27307,7 @@
       <c r="C21" s="79"/>
       <c r="D21" s="58"/>
       <c r="E21" s="84" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F21" s="84"/>
       <c r="G21" s="84"/>
@@ -27356,7 +27325,7 @@
       </c>
       <c r="D22" s="58"/>
       <c r="E22" s="84" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F22" s="84"/>
       <c r="G22" s="84"/>
@@ -27539,7 +27508,7 @@
     </row>
     <row r="36" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="84" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
       <c r="B36" s="84"/>
       <c r="C36" s="84"/>
@@ -27550,7 +27519,9 @@
       <c r="H36" s="45"/>
     </row>
     <row r="37" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="65"/>
+      <c r="A37" s="65" t="s">
+        <v>644</v>
+      </c>
       <c r="B37" s="66"/>
       <c r="C37" s="66"/>
       <c r="D37" s="66"/>
@@ -31230,7 +31201,7 @@
       <c r="F25" s="15"/>
       <c r="G25" s="15"/>
     </row>
-    <row r="26" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
         <v>574</v>
       </c>
@@ -31264,7 +31235,7 @@
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
     </row>
-    <row r="28" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>548</v>
       </c>
@@ -31281,7 +31252,7 @@
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
     </row>
-    <row r="29" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>550</v>
       </c>
